--- a/IPA_Files/test case/モバイルアプリ(Flutter)/【エネマネ】【UTテストケース作成】EMS-SW-01_施設検索画面スマホ/【エネマネ】【UT-Testcase】EMS-SW-01_施設検索画面スマホ.xlsx
+++ b/IPA_Files/test case/モバイルアプリ(Flutter)/【エネマネ】【UTテストケース作成】EMS-SW-01_施設検索画面スマホ/【エネマネ】【UT-Testcase】EMS-SW-01_施設検索画面スマホ.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" tabRatio="372" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11750" tabRatio="372" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="タイトル" sheetId="4" r:id="rId1"/>
@@ -677,7 +677,7 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -767,11 +767,95 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="5" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="6" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -779,103 +863,13 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="5" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="6" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1284,216 +1278,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="17" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="53" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="53" t="s">
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53" t="s">
+      <c r="M1" s="34"/>
+      <c r="N1" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="53"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A2" s="47"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="56" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56" t="s">
+      <c r="E2" s="35"/>
+      <c r="F2" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="66" t="s">
+      <c r="G2" s="35"/>
+      <c r="H2" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="56" t="s">
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="56"/>
-      <c r="N2" s="68">
+      <c r="M2" s="35"/>
+      <c r="N2" s="38">
         <v>46049</v>
       </c>
-      <c r="O2" s="56"/>
+      <c r="O2" s="35"/>
     </row>
     <row r="3" spans="1:15" s="17" customFormat="1" ht="14">
-      <c r="A3" s="47"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="53" t="s">
+      <c r="A3" s="55"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="55" t="s">
+      <c r="E3" s="34"/>
+      <c r="F3" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55" t="s">
+      <c r="G3" s="62"/>
+      <c r="H3" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="53" t="s">
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53" t="s">
+      <c r="M3" s="34"/>
+      <c r="N3" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="53"/>
+      <c r="O3" s="34"/>
     </row>
     <row r="4" spans="1:15" s="17" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="56" t="s">
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="56"/>
-      <c r="N4" s="68">
+      <c r="M4" s="35"/>
+      <c r="N4" s="38">
         <v>46058</v>
       </c>
-      <c r="O4" s="56"/>
+      <c r="O4" s="35"/>
     </row>
     <row r="5" spans="1:15" s="18" customFormat="1" ht="21" customHeight="1"/>
     <row r="6" spans="1:15" s="18" customFormat="1" ht="13.5" customHeight="1">
       <c r="A6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="39"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="63"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="49"/>
       <c r="G6" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
     </row>
     <row r="7" spans="1:15" s="18" customFormat="1" ht="33" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="59" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
     </row>
     <row r="8" spans="1:15" s="18" customFormat="1" ht="27" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="59" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="59"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
     </row>
     <row r="9" spans="1:15" s="18" customFormat="1" ht="20" customHeight="1">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="41" t="s">
+      <c r="B9" s="44"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
     </row>
     <row r="10" spans="1:15" s="18" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="41" t="s">
+      <c r="B10" s="44"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
     </row>
     <row r="11" spans="1:15" s="16" customFormat="1" ht="14"/>
     <row r="12" spans="1:15" s="25" customFormat="1" ht="13.75" customHeight="1">
@@ -1507,13 +1501,13 @@
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:15" s="25" customFormat="1" ht="26" customHeight="1">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="43"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="21"/>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
@@ -1521,7 +1515,7 @@
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:15" s="25" customFormat="1" ht="31" customHeight="1">
-      <c r="A14" s="36"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="29" t="s">
         <v>59</v>
       </c>
@@ -1699,7 +1693,7 @@
       <c r="C19" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="12" t="s">
         <v>80</v>
       </c>
       <c r="E19" s="14" t="s">
@@ -1730,7 +1724,7 @@
       <c r="C20" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="12" t="s">
         <v>79</v>
       </c>
       <c r="E20" s="14" t="s">
@@ -1807,13 +1801,21 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="A8:C8"/>
@@ -1830,21 +1832,13 @@
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
